--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2022_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2022_aysen.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:36</t>
+    <t xml:space="preserve">2026-09-24 01:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -973,7 +973,7 @@
         <v>-0.4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.23</v>
@@ -993,10 +993,10 @@
         <v>9</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.32</v>
@@ -1019,7 +1019,7 @@
         <v>-0.32</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.15</v>
@@ -1033,19 +1033,19 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="23">
@@ -1079,19 +1079,19 @@
         <v>34</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.09</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.48</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="25">
@@ -1102,19 +1102,19 @@
         <v>34</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="26">
@@ -1125,19 +1125,19 @@
         <v>34</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.63</v>
+        <v>0.36</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.3</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2022_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2022_aysen.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:26</t>
+    <t xml:space="preserve">2026-10-01 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2022_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2022_aysen.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:09</t>
+    <t xml:space="preserve">2026-10-05 19:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
